--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/SOUTH_CAROLINA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/SOUTH_CAROLINA_2011.xlsx
@@ -535,7 +535,7 @@
         <v>8</v>
       </c>
       <c r="D10">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="11">
@@ -625,7 +625,7 @@
         <v>8</v>
       </c>
       <c r="D15">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="16">
@@ -1021,7 +1021,7 @@
         <v>8</v>
       </c>
       <c r="D37">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="38">
@@ -1633,7 +1633,7 @@
         <v>8</v>
       </c>
       <c r="D71">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="72">
@@ -2587,7 +2587,7 @@
         <v>8</v>
       </c>
       <c r="D124">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="125">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C134">
@@ -3019,7 +3019,7 @@
         <v>8</v>
       </c>
       <c r="D148">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="149">
@@ -3469,7 +3469,7 @@
         <v>8</v>
       </c>
       <c r="D173">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="174">
@@ -4315,7 +4315,7 @@
         <v>8</v>
       </c>
       <c r="D220">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="221">
@@ -4549,7 +4549,7 @@
         <v>8</v>
       </c>
       <c r="D233">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="234">
@@ -4855,7 +4855,7 @@
         <v>8</v>
       </c>
       <c r="D250">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="251">
@@ -5539,7 +5539,7 @@
         <v>8</v>
       </c>
       <c r="D288">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="289">
@@ -6061,7 +6061,7 @@
         <v>8</v>
       </c>
       <c r="D317">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="318">
@@ -6169,7 +6169,7 @@
         <v>8</v>
       </c>
       <c r="D323">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="324">
@@ -6871,7 +6871,7 @@
         <v>8</v>
       </c>
       <c r="D362">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="363">
@@ -8059,7 +8059,7 @@
         <v>8</v>
       </c>
       <c r="D428">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="429">
@@ -8653,7 +8653,7 @@
         <v>8</v>
       </c>
       <c r="D461">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="462">
@@ -8869,7 +8869,7 @@
         <v>8</v>
       </c>
       <c r="D473">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="474">
@@ -9067,7 +9067,7 @@
         <v>8</v>
       </c>
       <c r="D484">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="485">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C521">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C579">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C595">
@@ -12649,7 +12649,7 @@
         <v>8</v>
       </c>
       <c r="D683">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="684">
@@ -13459,7 +13459,7 @@
         <v>8</v>
       </c>
       <c r="D728">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="729">
@@ -13549,7 +13549,7 @@
         <v>8</v>
       </c>
       <c r="D733">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="734">
@@ -14521,7 +14521,7 @@
         <v>8</v>
       </c>
       <c r="D787">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="788">
@@ -14773,7 +14773,7 @@
         <v>8</v>
       </c>
       <c r="D801">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="802">
@@ -15871,7 +15871,7 @@
         <v>8</v>
       </c>
       <c r="D862">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="863">
@@ -15961,7 +15961,7 @@
         <v>8</v>
       </c>
       <c r="D867">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="868">
@@ -16087,7 +16087,7 @@
         <v>8</v>
       </c>
       <c r="D874">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="875">
@@ -16177,7 +16177,7 @@
         <v>8</v>
       </c>
       <c r="D879">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="880">
@@ -16609,7 +16609,7 @@
         <v>8</v>
       </c>
       <c r="D903">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="904">
@@ -16789,7 +16789,7 @@
         <v>8</v>
       </c>
       <c r="D913">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="914">
@@ -16987,7 +16987,7 @@
         <v>8</v>
       </c>
       <c r="D924">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="925">
@@ -17455,7 +17455,7 @@
         <v>8</v>
       </c>
       <c r="D950">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="951">
@@ -18132,7 +18132,7 @@
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C988">
@@ -18265,7 +18265,7 @@
         <v>8</v>
       </c>
       <c r="D995">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="996">
@@ -18283,7 +18283,7 @@
         <v>8</v>
       </c>
       <c r="D996">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="997">
@@ -18463,7 +18463,7 @@
         <v>8</v>
       </c>
       <c r="D1006">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="1007">
@@ -18499,7 +18499,7 @@
         <v>8</v>
       </c>
       <c r="D1008">
-        <v>0.000942729201037</v>
+        <v>0.0009427292010370002</v>
       </c>
     </row>
     <row r="1009">
